--- a/customer_satisfaction_evaluation_forms/002_retail_product_delivery_satisfaction_survey--customer_satisfaction_evaluation_forms.xlsx
+++ b/customer_satisfaction_evaluation_forms/002_retail_product_delivery_satisfaction_survey--customer_satisfaction_evaluation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -784,8 +784,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -813,12 +813,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'very_satisfied',_'value':_5}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Very Satisfied', 'value': 5}</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
@@ -830,12 +830,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_satisfied',_'value':_4}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Satisfied', 'value': 4}</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
@@ -847,12 +847,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'neutral',_'value':_3}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral', 'value': 3}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -864,12 +864,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_dissatisfied',_'value':_2}</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Dissatisfied', 'value': 2}</t>
+          <t>Somewhat Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -881,12 +881,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'very_dissatisfied',_'value':_1}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Very Dissatisfied', 'value': 1}</t>
+          <t>Very Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -898,12 +898,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'very_clear',_'value':_5}</t>
+          <t>very_clear</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Very Clear', 'value': 5}</t>
+          <t>Very Clear</t>
         </is>
       </c>
     </row>
@@ -915,12 +915,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_clear',_'value':_4}</t>
+          <t>somewhat_clear</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Clear', 'value': 4}</t>
+          <t>Somewhat Clear</t>
         </is>
       </c>
     </row>
@@ -932,12 +932,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'neutral',_'value':_3}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral', 'value': 3}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -949,12 +949,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_unclear',_'value':_2}</t>
+          <t>somewhat_unclear</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Unclear', 'value': 2}</t>
+          <t>Somewhat Unclear</t>
         </is>
       </c>
     </row>
@@ -966,12 +966,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'not_clear',_'value':_1}</t>
+          <t>not_clear</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Not Clear', 'value': 1}</t>
+          <t>Not Clear</t>
         </is>
       </c>
     </row>
@@ -983,12 +983,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'on_time',_'value':_'on_time'}</t>
+          <t>on_time</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'On Time', 'value': 'on_time'}</t>
+          <t>On Time</t>
         </is>
       </c>
     </row>
@@ -1000,12 +1000,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'late',_'value':_'late'}</t>
+          <t>late</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Late', 'value': 'late'}</t>
+          <t>Late</t>
         </is>
       </c>
     </row>
@@ -1017,12 +1017,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'not_on_time',_'value':_'not_on_time'}</t>
+          <t>not_on_time</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Not on Time', 'value': 'not_on_time'}</t>
+          <t>Not on Time</t>
         </is>
       </c>
     </row>
@@ -1034,12 +1034,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'very_reliable',_'value':_5}</t>
+          <t>very_reliable</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Very Reliable', 'value': 5}</t>
+          <t>Very Reliable</t>
         </is>
       </c>
     </row>
@@ -1051,12 +1051,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_reliable',_'value':_4}</t>
+          <t>somewhat_reliable</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Reliable', 'value': 4}</t>
+          <t>Somewhat Reliable</t>
         </is>
       </c>
     </row>
@@ -1068,12 +1068,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'neutral',_'value':_3}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral', 'value': 3}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1085,12 +1085,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_unreliable',_'value':_2}</t>
+          <t>somewhat_unreliable</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Unreliable', 'value': 2}</t>
+          <t>Somewhat Unreliable</t>
         </is>
       </c>
     </row>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'not_reliable',_'value':_1}</t>
+          <t>not_reliable</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Not Reliable', 'value': 1}</t>
+          <t>Not Reliable</t>
         </is>
       </c>
     </row>
@@ -1119,12 +1119,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'very_often',_'value':_5}</t>
+          <t>very_often</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Very Often', 'value': 5}</t>
+          <t>Very Often</t>
         </is>
       </c>
     </row>
@@ -1136,12 +1136,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_often',_'value':_4}</t>
+          <t>somewhat_often</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Often', 'value': 4}</t>
+          <t>Somewhat Often</t>
         </is>
       </c>
     </row>
@@ -1153,12 +1153,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'neutral',_'value':_3}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral', 'value': 3}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_not_often',_'value':_2}</t>
+          <t>somewhat_not_often</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Not Often', 'value': 2}</t>
+          <t>Somewhat Not Often</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'not_often',_'value':_1}</t>
+          <t>not_often</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Not Often', 'value': 1}</t>
+          <t>Not Often</t>
         </is>
       </c>
     </row>
@@ -1204,12 +1204,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'no_complaints',_'value':_'no_complaints'}</t>
+          <t>no_complaints</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'No Complaints', 'value': 'no_complaints'}</t>
+          <t>No Complaints</t>
         </is>
       </c>
     </row>
@@ -1221,12 +1221,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'some_complaints',_'value':_'some_complaints'}</t>
+          <t>some_complaints</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Some Complaints', 'value': 'some_complaints'}</t>
+          <t>Some Complaints</t>
         </is>
       </c>
     </row>
@@ -1238,12 +1238,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'many_complaints',_'value':_'many_complains'}</t>
+          <t>many_complaints</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Many Complaints', 'value': 'many_complains'}</t>
+          <t>Many Complaints</t>
         </is>
       </c>
     </row>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'on_time',_'value':_'on_time'}</t>
+          <t>on_time</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'On Time', 'value': 'on_time'}</t>
+          <t>On Time</t>
         </is>
       </c>
     </row>
@@ -1272,12 +1272,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'late',_'value':_'late'}</t>
+          <t>late</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Late', 'value': 'late'}</t>
+          <t>Late</t>
         </is>
       </c>
     </row>
@@ -1289,12 +1289,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'not_on_time',_'value':_'not_on_time'}</t>
+          <t>not_on_time</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'Not on Time', 'value': 'not_on_time'}</t>
+          <t>Not on Time</t>
         </is>
       </c>
     </row>
